--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/RegistroEliminado.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/RegistroEliminado.xlsx
@@ -618,12 +618,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>YV2XG6ZA7RE900101</t>
+          <t>YV2XG6ZA7RE284211</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>E900101</t>
+          <t>E284211</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>317802015</t>
+          <t>773747253</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9900000078</t>
+          <t>8227547240</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9BVK20AA5SE900001</t>
+          <t>9BVK20AA5SE640524</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>E900001</t>
+          <t>E640524</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>315822266</t>
+          <t>76464462K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>9900000055</t>
+          <t>5716095802</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9BVRB40A8PA900010</t>
+          <t>9BVRB40A8PA873777</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A900010</t>
+          <t>A873777</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>315743071</t>
+          <t>764451589</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>9900000003</t>
+          <t>1315393763</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9900000051</t>
+          <t>5092891721</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>+56999000036</t>
+          <t>+56933457421</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
